--- a/docs/Lab02/Lab02_BBT_TCs_Form_bun.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form_bun.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5C988D-E594-446B-9A23-06780BB14746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FE1E3F-5F27-48F9-989D-43D20620D9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -1500,215 +1500,215 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2165,12 +2165,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="59"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
       <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
@@ -2178,11 +2178,11 @@
       <c r="J1" s="36"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H2" s="92" t="s">
+      <c r="H2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H3" s="2"/>
@@ -2341,21 +2341,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="33"/>
-      <c r="B24" s="91" t="s">
+      <c r="B24" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="91"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="91"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C26" s="35"/>
@@ -2440,21 +2440,21 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B41" s="91" t="s">
+      <c r="B41" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="91"/>
-      <c r="I41" s="91"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="91"/>
-      <c r="L41" s="91"/>
-      <c r="M41" s="91"/>
-      <c r="N41" s="91"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="52"/>
+      <c r="K41" s="52"/>
+      <c r="L41" s="52"/>
+      <c r="M41" s="52"/>
+      <c r="N41" s="52"/>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B42" s="39" t="s">
@@ -2514,41 +2514,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="59"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="101"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="77"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="G5" s="93" t="s">
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="G5" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-      <c r="K5" s="94"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="94"/>
-      <c r="N5" s="94"/>
-      <c r="O5" s="95"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="72"/>
       <c r="Q5" s="45"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
@@ -2564,37 +2564,37 @@
       <c r="E6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="60" t="s">
+      <c r="H6" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="54" t="s">
+      <c r="I6" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="54" t="s">
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="56"/>
+      <c r="O6" s="66"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="96" t="s">
+      <c r="C7" s="68" t="s">
         <v>89</v>
       </c>
       <c r="D7" s="42" t="s">
         <v>105</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="110"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="64"/>
       <c r="I7" s="12" t="s">
         <v>90</v>
       </c>
@@ -2610,16 +2610,16 @@
       <c r="M7" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="N7" s="54" t="s">
+      <c r="N7" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="56"/>
+      <c r="O7" s="66"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="97"/>
+      <c r="C8" s="73"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>86</v>
@@ -2645,16 +2645,16 @@
       <c r="M8" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="N8" s="103" t="s">
+      <c r="N8" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="O8" s="104"/>
+      <c r="O8" s="60"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="97"/>
+      <c r="C9" s="73"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
         <v>87</v>
@@ -2680,16 +2680,16 @@
       <c r="M9" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="N9" s="103" t="s">
+      <c r="N9" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="O9" s="104"/>
+      <c r="O9" s="60"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="97"/>
+      <c r="C10" s="73"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>88</v>
@@ -2715,16 +2715,16 @@
       <c r="M10" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="N10" s="103" t="s">
+      <c r="N10" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="O10" s="104"/>
+      <c r="O10" s="60"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="98"/>
+      <c r="C11" s="69"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
         <v>106</v>
@@ -2750,16 +2750,16 @@
       <c r="M11" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="N11" s="103" t="s">
+      <c r="N11" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="O11" s="104"/>
+      <c r="O11" s="60"/>
     </row>
     <row r="12" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="105" t="s">
+      <c r="C12" s="67" t="s">
         <v>83</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -2787,16 +2787,16 @@
       <c r="M12" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="N12" s="103" t="s">
+      <c r="N12" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="O12" s="104"/>
+      <c r="O12" s="60"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="105"/>
+      <c r="C13" s="67"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
         <v>85</v>
@@ -2810,14 +2810,14 @@
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
-      <c r="N13" s="106"/>
-      <c r="O13" s="107"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="62"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="96"/>
+      <c r="C14" s="68"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="G14" s="11"/>
@@ -2827,14 +2827,14 @@
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
-      <c r="N14" s="108"/>
-      <c r="O14" s="109"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="58"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="98"/>
+      <c r="C15" s="69"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="G15" s="11"/>
@@ -2844,14 +2844,14 @@
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
-      <c r="N15" s="108"/>
-      <c r="O15" s="109"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="58"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="105"/>
+      <c r="C16" s="67"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="11"/>
@@ -2861,14 +2861,14 @@
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
-      <c r="N16" s="108"/>
-      <c r="O16" s="109"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="58"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="105"/>
+      <c r="C17" s="67"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="G17" s="11"/>
@@ -2878,14 +2878,14 @@
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
       <c r="M17" s="10"/>
-      <c r="N17" s="108"/>
-      <c r="O17" s="109"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="58"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="105"/>
+      <c r="C18" s="67"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="11"/>
@@ -2895,14 +2895,14 @@
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
       <c r="M18" s="10"/>
-      <c r="N18" s="108"/>
-      <c r="O18" s="109"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="58"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="105"/>
+      <c r="C19" s="67"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="G19" s="12"/>
@@ -2912,14 +2912,14 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="109"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="58"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="105"/>
+      <c r="C20" s="67"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
@@ -2927,7 +2927,7 @@
       <c r="B21" s="4">
         <v>15</v>
       </c>
-      <c r="C21" s="105"/>
+      <c r="C21" s="67"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
     </row>
@@ -2942,24 +2942,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C18:C19"/>
     <mergeCell ref="G5:O5"/>
     <mergeCell ref="C7:C11"/>
     <mergeCell ref="I6:M6"/>
@@ -2969,6 +2951,24 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="N11:O11"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N15:O15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3000,43 +3000,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="59"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="101"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="77"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="114" t="s">
+      <c r="B5" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="116" t="s">
+      <c r="G5" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
     </row>
     <row r="6" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
@@ -3049,44 +3049,44 @@
         <v>40</v>
       </c>
       <c r="E6" s="7"/>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="H6" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="68" t="s">
+      <c r="I6" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="60" t="s">
+      <c r="J6" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="119" t="s">
+      <c r="K6" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="121"/>
-      <c r="M6" s="121"/>
-      <c r="N6" s="121"/>
-      <c r="O6" s="121"/>
-      <c r="P6" s="119" t="s">
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="120"/>
+      <c r="Q6" s="88"/>
     </row>
     <row r="7" spans="2:17" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="96">
+      <c r="B7" s="68">
         <v>1</v>
       </c>
-      <c r="C7" s="111" t="s">
+      <c r="C7" s="89" t="s">
         <v>102</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="110"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="64"/>
       <c r="K7" s="12" t="s">
         <v>90</v>
       </c>
@@ -3102,14 +3102,14 @@
       <c r="O7" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="P7" s="54" t="s">
+      <c r="P7" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="Q7" s="56"/>
+      <c r="Q7" s="66"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="97"/>
-      <c r="C8" s="112"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="90"/>
       <c r="D8" s="2" t="s">
         <v>103</v>
       </c>
@@ -3140,14 +3140,14 @@
       <c r="O8" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="P8" s="103" t="s">
+      <c r="P8" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="Q8" s="104"/>
+      <c r="Q8" s="60"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B9" s="97"/>
-      <c r="C9" s="112"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="90"/>
       <c r="D9" s="2" t="s">
         <v>123</v>
       </c>
@@ -3178,14 +3178,14 @@
       <c r="O9" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="P9" s="103" t="s">
+      <c r="P9" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="Q9" s="104"/>
+      <c r="Q9" s="60"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="97"/>
-      <c r="C10" s="112"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="90"/>
       <c r="D10" s="2" t="s">
         <v>113</v>
       </c>
@@ -3216,14 +3216,14 @@
       <c r="O10" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="103" t="s">
+      <c r="P10" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="Q10" s="104"/>
+      <c r="Q10" s="60"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="97"/>
-      <c r="C11" s="112"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="90"/>
       <c r="D11" s="2" t="s">
         <v>114</v>
       </c>
@@ -3252,14 +3252,14 @@
       <c r="O11" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="103" t="s">
+      <c r="P11" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="Q11" s="104"/>
+      <c r="Q11" s="60"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="98"/>
-      <c r="C12" s="113"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="91"/>
       <c r="D12" s="2" t="s">
         <v>115</v>
       </c>
@@ -3290,16 +3290,16 @@
       <c r="O12" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="P12" s="103" t="s">
+      <c r="P12" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="Q12" s="104"/>
+      <c r="Q12" s="60"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="96">
+      <c r="B13" s="68">
         <v>2</v>
       </c>
-      <c r="C13" s="96" t="s">
+      <c r="C13" s="68" t="s">
         <v>101</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -3332,14 +3332,14 @@
       <c r="O13" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="P13" s="103" t="s">
+      <c r="P13" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="Q13" s="104"/>
+      <c r="Q13" s="60"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="97"/>
-      <c r="C14" s="97"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
       <c r="D14" s="2" t="s">
         <v>117</v>
       </c>
@@ -3374,8 +3374,8 @@
       <c r="Q14" s="38"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="97"/>
-      <c r="C15" s="97"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
       <c r="D15" s="2" t="s">
         <v>118</v>
       </c>
@@ -3388,12 +3388,12 @@
       <c r="M15" s="21"/>
       <c r="N15" s="21"/>
       <c r="O15" s="21"/>
-      <c r="P15" s="103"/>
-      <c r="Q15" s="104"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="60"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="97"/>
-      <c r="C16" s="97"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
       <c r="D16" s="2" t="s">
         <v>119</v>
       </c>
@@ -3406,12 +3406,12 @@
       <c r="M16" s="21"/>
       <c r="N16" s="21"/>
       <c r="O16" s="21"/>
-      <c r="P16" s="103"/>
-      <c r="Q16" s="104"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="60"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="97"/>
-      <c r="C17" s="97"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
       <c r="D17" s="2" t="s">
         <v>120</v>
       </c>
@@ -3424,12 +3424,12 @@
       <c r="M17" s="21"/>
       <c r="N17" s="21"/>
       <c r="O17" s="21"/>
-      <c r="P17" s="103"/>
-      <c r="Q17" s="104"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="60"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="98"/>
-      <c r="C18" s="98"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
       <c r="D18" s="2" t="s">
         <v>121</v>
       </c>
@@ -3442,14 +3442,14 @@
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
       <c r="O18" s="21"/>
-      <c r="P18" s="103"/>
-      <c r="Q18" s="104"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="60"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="96">
+      <c r="B19" s="68">
         <v>3</v>
       </c>
-      <c r="C19" s="111"/>
+      <c r="C19" s="89"/>
       <c r="D19" s="2"/>
       <c r="G19" s="40"/>
       <c r="H19" s="44"/>
@@ -3460,12 +3460,12 @@
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
       <c r="O19" s="21"/>
-      <c r="P19" s="103"/>
-      <c r="Q19" s="104"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="60"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="97"/>
-      <c r="C20" s="112"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="90"/>
       <c r="D20" s="2"/>
       <c r="G20" s="40"/>
       <c r="H20" s="44"/>
@@ -3476,12 +3476,12 @@
       <c r="M20" s="21"/>
       <c r="N20" s="21"/>
       <c r="O20" s="21"/>
-      <c r="P20" s="103"/>
-      <c r="Q20" s="104"/>
+      <c r="P20" s="59"/>
+      <c r="Q20" s="60"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="97"/>
-      <c r="C21" s="112"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="90"/>
       <c r="D21" s="2"/>
       <c r="G21" s="40"/>
       <c r="H21" s="44"/>
@@ -3492,12 +3492,12 @@
       <c r="M21" s="21"/>
       <c r="N21" s="21"/>
       <c r="O21" s="21"/>
-      <c r="P21" s="103"/>
-      <c r="Q21" s="104"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="97"/>
-      <c r="C22" s="112"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="90"/>
       <c r="D22" s="2"/>
       <c r="G22" s="40"/>
       <c r="H22" s="44"/>
@@ -3508,79 +3508,75 @@
       <c r="M22" s="21"/>
       <c r="N22" s="21"/>
       <c r="O22" s="21"/>
-      <c r="P22" s="103"/>
-      <c r="Q22" s="104"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="60"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="97"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B24" s="98"/>
-      <c r="C24" s="113"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="91"/>
       <c r="D24" s="2"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B25" s="96">
+      <c r="B25" s="68">
         <v>4</v>
       </c>
-      <c r="C25" s="111"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="2"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="117"/>
-      <c r="I25" s="118"/>
-      <c r="J25" s="118"/>
-      <c r="K25" s="118"/>
-      <c r="L25" s="118"/>
-      <c r="M25" s="118"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="87"/>
+      <c r="K25" s="87"/>
+      <c r="L25" s="87"/>
+      <c r="M25" s="87"/>
       <c r="N25" s="28"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B26" s="97"/>
-      <c r="C26" s="112"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="90"/>
       <c r="D26" s="2"/>
-      <c r="I26" s="115"/>
-      <c r="J26" s="115"/>
-      <c r="K26" s="115"/>
-      <c r="L26" s="115"/>
-      <c r="M26" s="115"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
       <c r="N26" s="29"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="97"/>
-      <c r="C27" s="112"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="90"/>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B28" s="97"/>
-      <c r="C28" s="112"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="90"/>
       <c r="D28" s="2"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B29" s="97"/>
-      <c r="C29" s="112"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="90"/>
       <c r="D29" s="2"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B30" s="98"/>
-      <c r="C30" s="113"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="91"/>
       <c r="D30" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="I26:M26"/>
     <mergeCell ref="B1:E1"/>
@@ -3597,14 +3593,18 @@
     <mergeCell ref="P22:Q22"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3632,58 +3632,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="59"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="107" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55" t="s">
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="56"/>
+      <c r="L4" s="66"/>
     </row>
     <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="69"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="61"/>
+      <c r="B5" s="106"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="120"/>
       <c r="F5" s="12" t="s">
         <v>90</v>
       </c>
@@ -3710,7 +3710,7 @@
       <c r="B6" s="13">
         <v>1</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="102" t="s">
         <v>54</v>
       </c>
       <c r="D6" s="18" t="s">
@@ -3746,7 +3746,7 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="65"/>
+      <c r="C7" s="103"/>
       <c r="D7" s="19" t="s">
         <v>132</v>
       </c>
@@ -3780,7 +3780,7 @@
         <f t="shared" ref="B8:B12" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="65"/>
+      <c r="C8" s="103"/>
       <c r="D8" s="19" t="s">
         <v>56</v>
       </c>
@@ -3814,7 +3814,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="65"/>
+      <c r="C9" s="103"/>
       <c r="D9" s="18" t="s">
         <v>134</v>
       </c>
@@ -3848,7 +3848,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="65"/>
+      <c r="C10" s="103"/>
       <c r="D10" s="19" t="s">
         <v>57</v>
       </c>
@@ -3882,7 +3882,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="65"/>
+      <c r="C11" s="103"/>
       <c r="D11" s="19" t="s">
         <v>35</v>
       </c>
@@ -3916,7 +3916,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="65"/>
+      <c r="C12" s="103"/>
       <c r="D12" s="19" t="s">
         <v>35</v>
       </c>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="48"/>
-      <c r="C13" s="65"/>
+      <c r="C13" s="103"/>
       <c r="D13" s="47"/>
       <c r="E13" s="48" t="s">
         <v>137</v>
@@ -3979,7 +3979,7 @@
         <f>B12+1</f>
         <v>8</v>
       </c>
-      <c r="C14" s="66"/>
+      <c r="C14" s="104"/>
       <c r="D14" s="20" t="s">
         <v>34</v>
       </c>
@@ -4035,98 +4035,98 @@
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="67"/>
+      <c r="K16" s="105"/>
+      <c r="L16" s="105"/>
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M17" s="5"/>
     </row>
     <row r="18" spans="2:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="78" t="s">
+      <c r="C18" s="96" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="80"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="99"/>
       <c r="G18" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="H18" s="78" t="s">
+      <c r="H18" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="I18" s="81"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="80"/>
-      <c r="M18" s="78" t="s">
+      <c r="I18" s="97"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="98"/>
+      <c r="L18" s="99"/>
+      <c r="M18" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="N18" s="81"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="80"/>
+      <c r="N18" s="97"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="99"/>
     </row>
     <row r="19" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="75" t="s">
+      <c r="C19" s="112" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="76" t="s">
+      <c r="D19" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="76" t="s">
+      <c r="E19" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="77" t="s">
+      <c r="F19" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="86" t="s">
+      <c r="G19" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="82" t="s">
+      <c r="H19" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="83"/>
-      <c r="J19" s="76" t="s">
+      <c r="I19" s="114"/>
+      <c r="J19" s="94" t="s">
         <v>63</v>
       </c>
-      <c r="K19" s="68" t="s">
+      <c r="K19" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="L19" s="62" t="s">
+      <c r="L19" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="M19" s="89" t="s">
+      <c r="M19" s="100" t="s">
         <v>68</v>
       </c>
-      <c r="N19" s="76" t="s">
+      <c r="N19" s="94" t="s">
         <v>63</v>
       </c>
-      <c r="O19" s="76" t="s">
+      <c r="O19" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="P19" s="77" t="s">
+      <c r="P19" s="95" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B20" s="74"/>
-      <c r="C20" s="75"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="76"/>
-      <c r="K20" s="87"/>
-      <c r="L20" s="88"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="76"/>
-      <c r="O20" s="76"/>
-      <c r="P20" s="77"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="94"/>
+      <c r="E20" s="94"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="116"/>
+      <c r="J20" s="94"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="101"/>
+      <c r="N20" s="94"/>
+      <c r="O20" s="94"/>
+      <c r="P20" s="95"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="27" t="s">
@@ -4136,10 +4136,10 @@
         <v>9</v>
       </c>
       <c r="D21" s="25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" s="26">
         <v>1</v>
@@ -4147,15 +4147,15 @@
       <c r="G21" s="31">
         <v>1</v>
       </c>
-      <c r="H21" s="72" t="s">
+      <c r="H21" s="109" t="s">
         <v>140</v>
       </c>
-      <c r="I21" s="73"/>
+      <c r="I21" s="110"/>
       <c r="J21" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L21" s="26">
         <v>0</v>
@@ -4164,10 +4164,10 @@
         <v>140</v>
       </c>
       <c r="N21" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" s="25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P21" s="26">
         <v>0</v>
@@ -4178,12 +4178,12 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="P19:P20"/>
-    <mergeCell ref="M18:P18"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
     <mergeCell ref="C6:C14"/>
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="B4:B5"/>
@@ -4200,12 +4200,12 @@
     <mergeCell ref="H19:I20"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="K19:K20"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:N20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4215,6 +4215,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4352,22 +4367,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4383,21 +4400,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>